--- a/Result/profitability/3653.xlsx
+++ b/Result/profitability/3653.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>7.60375</v>
+        <v>8.904999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>38.965</v>
+        <v>40.05</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>7.08875</v>
+        <v>8.1</v>
       </c>
       <c r="N3" t="n">
-        <v>37.7525</v>
+        <v>38.8875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>6.32625</v>
+        <v>7.102499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>36.2025</v>
+        <v>36.44</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>5.281249999999999</v>
+        <v>6.275</v>
       </c>
       <c r="N5" t="n">
-        <v>34.02875</v>
+        <v>34.695</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>4.39125</v>
+        <v>5.18</v>
       </c>
       <c r="N6" t="n">
-        <v>31.75625</v>
+        <v>32.73625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.63</v>
       </c>
       <c r="M7" t="n">
-        <v>3.28375</v>
+        <v>4.015</v>
       </c>
       <c r="N7" t="n">
-        <v>29.95125</v>
+        <v>30.64625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>2.29</v>
       </c>
       <c r="M8" t="n">
-        <v>2.32625</v>
+        <v>3.11</v>
       </c>
       <c r="N8" t="n">
-        <v>29.7275</v>
+        <v>30.35625</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7275</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3870</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3405</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2749</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>37.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>92</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2841</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2318</v>
+      </c>
+      <c r="L75" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M75" t="n">
+        <v>9.41375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>41.3825</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>6.270000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6579223504721932</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.030000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1203925323121111</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>7.950000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.012738853503185</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.330000000000005</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1284956605593057</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
